--- a/src/pandorafits/formats/visda/level0_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0_visda.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chedges/Pandora/repos/pandora-fits/src/pandorafits/formats/visda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4D4843-2CD8-344B-B9B8-7FC25771DCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7291F594-648E-7F40-B82D-D1619AF5AE03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17260" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17220" activeTab="5" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
   </bookViews>
   <sheets>
     <sheet name="Structure" sheetId="7" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="139">
   <si>
     <t>SIMPLE</t>
   </si>
@@ -244,9 +244,6 @@
     <t>TFORM2</t>
   </si>
   <si>
-    <t>TUNIT2</t>
-  </si>
-  <si>
     <t>TBCOL2</t>
   </si>
   <si>
@@ -280,9 +277,6 @@
     <t>Column</t>
   </si>
   <si>
-    <t>units: pixels</t>
-  </si>
-  <si>
     <t>Row</t>
   </si>
   <si>
@@ -310,12 +304,6 @@
     <t>Temperature</t>
   </si>
   <si>
-    <t>ms</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
     <t>TEMP_TIME</t>
   </si>
   <si>
@@ -326,9 +314,6 @@
   </si>
   <si>
     <t>TFORM3</t>
-  </si>
-  <si>
-    <t>TUNIT3</t>
   </si>
   <si>
     <t>TBCOL3</t>
@@ -897,13 +882,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -911,7 +896,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C2" t="b">
         <v>0</v>
@@ -922,7 +907,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C3" t="b">
         <v>0</v>
@@ -930,10 +915,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C4" t="b">
         <v>0</v>
@@ -941,10 +926,10 @@
     </row>
     <row r="5" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
@@ -952,10 +937,10 @@
     </row>
     <row r="6" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -982,10 +967,10 @@
         <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
@@ -1107,16 +1092,16 @@
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -1138,7 +1123,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
         <v>41</v>
@@ -1149,7 +1134,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
         <v>42</v>
@@ -1157,40 +1142,40 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B18">
         <v>32</v>
@@ -1201,13 +1186,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -1256,90 +1241,90 @@
     </row>
     <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>9</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C25">
         <v>50</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C26" s="4">
         <v>65</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C27">
         <v>50</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C28">
         <v>512</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C29">
         <v>512</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C30" s="2">
         <v>1024</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C31">
         <v>1024</v>
       </c>
       <c r="D31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1350,7 +1335,7 @@
         <v>200000</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -1377,13 +1362,13 @@
     </row>
     <row r="35" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -1558,10 +1543,10 @@
         <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
@@ -1677,7 +1662,7 @@
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1688,7 +1673,7 @@
     </row>
     <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B12" s="4">
         <v>2147483648</v>
@@ -1702,13 +1687,13 @@
         <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1716,13 +1701,13 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1730,13 +1715,13 @@
         <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1760,10 +1745,10 @@
         <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
@@ -1774,10 +1759,10 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
         <v>55</v>
@@ -1883,13 +1868,13 @@
         <v>29</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1897,13 +1882,13 @@
         <v>30</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -1922,13 +1907,13 @@
         <v>65</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1936,18 +1921,18 @@
         <v>66</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15">
         <v>22</v>
@@ -1961,10 +1946,10 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
         <v>35</v>
@@ -1972,24 +1957,24 @@
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C17" s="2">
         <v>9</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C18" s="2">
         <v>50</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -2015,10 +2000,10 @@
         <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
@@ -2029,10 +2014,10 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
         <v>55</v>
@@ -2135,13 +2120,13 @@
         <v>29</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2149,13 +2134,13 @@
         <v>30</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -2174,13 +2159,13 @@
         <v>65</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2188,18 +2173,18 @@
         <v>66</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15">
         <v>195</v>
@@ -2213,10 +2198,10 @@
         <v>6</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
         <v>35</v>
@@ -2235,7 +2220,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4411FE80-4885-BE47-8AEB-14F721AB3195}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -2248,10 +2233,10 @@
         <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
@@ -2262,10 +2247,10 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
         <v>55</v>
@@ -2368,13 +2353,13 @@
         <v>29</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2382,157 +2367,115 @@
         <v>30</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3">
-        <v>1</v>
+        <v>65</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+      <c r="B15">
+        <v>26</v>
+      </c>
+      <c r="C15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17">
-        <v>26</v>
-      </c>
-      <c r="C17">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" t="s">
-        <v>80</v>
+        <v>91</v>
+      </c>
+      <c r="B18">
+        <v>51</v>
+      </c>
+      <c r="C18">
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>95</v>
-      </c>
-      <c r="B20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>96</v>
-      </c>
-      <c r="B21">
-        <v>51</v>
-      </c>
-      <c r="C21">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" t="s">
         <v>35</v>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0_visda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chedges/Pandora/repos/pandora-fits/src/pandorafits/formats/visda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D65050-2AC1-D048-AE7F-FB396CC1A452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC90912-6195-DD4A-B90D-913ADE5F90F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Structure" sheetId="1" r:id="rId1"/>

--- a/src/pandorafits/formats/visda/level0_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0_visda.xlsx
@@ -1262,12 +1262,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jQlIkOiHjOiHjOiH</t>
+          <t>iTkLjQhJiQhJiQhJ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:29</t>
+          <t>HDU checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:29</t>
+          <t>data unit checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TaCSVW9PTaCPTU9P</t>
+          <t>ScASUZ9SSaASSY9S</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:29</t>
+          <t>HDU checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:29</t>
+          <t>data unit checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ZemQfblQZblQdblQ</t>
+          <t>ZelTdekSZekSbekS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:29</t>
+          <t>HDU checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:29</t>
+          <t>data unit checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2358,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DfKGFeKFDeKFDeKF</t>
+          <t>CiJJEgJHCgJHCgJH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:29</t>
+          <t>HDU checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:29</t>
+          <t>data unit checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Upp7anm4Xnm4anm4</t>
+          <t>U3o7a0l7U0l7a0l7</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:29</t>
+          <t>HDU checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:29</t>
+          <t>data unit checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -4126,12 +4126,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FTaeFSYbFSabFSYb</t>
+          <t>EWaeEUWeEUaeEUWe</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:29</t>
+          <t>HDU checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:29</t>
+          <t>data unit checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0_visda.xlsx
@@ -1262,12 +1262,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>iTkLjQhJiQhJiQhJ</t>
+          <t>hSiKhQgJhQgJhQgJ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:50</t>
+          <t>HDU checksum updated 2026-01-08T14:07:55</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:50</t>
+          <t>data unit checksum updated 2026-01-08T14:07:55</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ScASUZ9SSaASSY9S</t>
+          <t>RbAUSZ8RRaARRY5R</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:50</t>
+          <t>HDU checksum updated 2026-01-08T14:07:55</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:50</t>
+          <t>data unit checksum updated 2026-01-08T14:07:55</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ZelTdekSZekSbekS</t>
+          <t>YgjSadjSZdjSadjS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:50</t>
+          <t>HDU checksum updated 2026-01-08T14:07:55</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:50</t>
+          <t>data unit checksum updated 2026-01-08T14:07:55</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2358,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CiJJEgJHCgJHCgJH</t>
+          <t>BhKICgHHBgHHBgHH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:50</t>
+          <t>HDU checksum updated 2026-01-08T14:07:55</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:50</t>
+          <t>data unit checksum updated 2026-01-08T14:07:55</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>U3o7a0l7U0l7a0l7</t>
+          <t>Y2m9a0k6T0k6Y0k6</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:50</t>
+          <t>HDU checksum updated 2026-01-08T14:07:55</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:50</t>
+          <t>data unit checksum updated 2026-01-08T14:07:55</t>
         </is>
       </c>
     </row>
@@ -4126,12 +4126,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EWaeEUWeEUaeEUWe</t>
+          <t>CVagFUVdCUZdCUZd</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:50</t>
+          <t>HDU checksum updated 2026-01-08T14:07:55</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:50</t>
+          <t>data unit checksum updated 2026-01-08T14:07:55</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0_visda.xlsx
@@ -1262,12 +1262,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>hSiKhQgJhQgJhQgJ</t>
+          <t>hSiKhRgKhRgKhRgK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:55</t>
+          <t>HDU checksum updated 2026-01-16T10:19:54</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:55</t>
+          <t>data unit checksum updated 2026-01-16T10:19:54</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RbAUSZ8RRaARRY5R</t>
+          <t>RcAUSZ8SRbASRZ5S</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:55</t>
+          <t>HDU checksum updated 2026-01-16T10:19:54</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:55</t>
+          <t>data unit checksum updated 2026-01-16T10:19:54</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>YgjSadjSZdjSadjS</t>
+          <t>YgjVaejSZejSaejS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:55</t>
+          <t>HDU checksum updated 2026-01-16T10:19:54</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:55</t>
+          <t>data unit checksum updated 2026-01-16T10:19:54</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2358,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BhKICgHHBgHHBgHH</t>
+          <t>BhKIChHIBhHIBhHI</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:55</t>
+          <t>HDU checksum updated 2026-01-16T10:19:54</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:55</t>
+          <t>data unit checksum updated 2026-01-16T10:19:54</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Y2m9a0k6T0k6Y0k6</t>
+          <t>Y2m9a1k7T1k7Y1k7</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:55</t>
+          <t>HDU checksum updated 2026-01-16T10:19:54</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:55</t>
+          <t>data unit checksum updated 2026-01-16T10:19:54</t>
         </is>
       </c>
     </row>
@@ -4126,12 +4126,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CVagFUVdCUZdCUZd</t>
+          <t>CVagFVVeCVZeCVZe</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:55</t>
+          <t>HDU checksum updated 2026-01-16T10:19:54</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:55</t>
+          <t>data unit checksum updated 2026-01-16T10:19:54</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0_visda.xlsx
@@ -1262,12 +1262,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>hSiKhRgKhRgKhRgK</t>
+          <t>kPkHmOkHkOkHkOkH</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:54</t>
+          <t>HDU checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:54</t>
+          <t>data unit checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RcAUSZ8SRbASRZ5S</t>
+          <t>UaFRXV9PUaEPUU9P</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:54</t>
+          <t>HDU checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:54</t>
+          <t>data unit checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>YgjVaejSZejSaejS</t>
+          <t>ZdoSibmPZbmPfbmP</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:54</t>
+          <t>HDU checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:54</t>
+          <t>data unit checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2358,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BhKIChHIBhHIBhHI</t>
+          <t>EeMFHeLFEeLFEeLF</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:54</t>
+          <t>HDU checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:54</t>
+          <t>data unit checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Y2m9a1k7T1k7Y1k7</t>
+          <t>Yoo6ano4Yno4ano4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:54</t>
+          <t>HDU checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:54</t>
+          <t>data unit checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -4126,12 +4126,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CVagFVVeCVZeCVZe</t>
+          <t>GScdHSZbGSbbGSZb</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:54</t>
+          <t>HDU checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:54</t>
+          <t>data unit checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0_visda.xlsx
@@ -1262,12 +1262,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>kPkHmOkHkOkHkOkH</t>
+          <t>iSjKiPhIiPhIiPhI</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:08</t>
+          <t>HDU checksum updated 2026-01-17T12:16:38</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:08</t>
+          <t>data unit checksum updated 2026-01-17T12:16:38</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UaFRXV9PUaEPUU9P</t>
+          <t>SaBRTZ9RSaARSW7R</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:08</t>
+          <t>HDU checksum updated 2026-01-17T12:16:38</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:08</t>
+          <t>data unit checksum updated 2026-01-17T12:16:38</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ZdoSibmPZbmPfbmP</t>
+          <t>ZdkScdkRZdkRbdkR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:08</t>
+          <t>HDU checksum updated 2026-01-17T12:16:38</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:08</t>
+          <t>data unit checksum updated 2026-01-17T12:16:38</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2358,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EeMFHeLFEeLFEeLF</t>
+          <t>ChLIDfIGCfIGCfIG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:08</t>
+          <t>HDU checksum updated 2026-01-17T12:16:38</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:08</t>
+          <t>data unit checksum updated 2026-01-17T12:16:38</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yoo6ano4Yno4ano4</t>
+          <t>Zrn6aol6Uol6Zol6</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:08</t>
+          <t>HDU checksum updated 2026-01-17T12:16:38</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:08</t>
+          <t>data unit checksum updated 2026-01-17T12:16:38</t>
         </is>
       </c>
     </row>
@@ -4126,12 +4126,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GScdHSZbGSbbGSZb</t>
+          <t>DVadGTXdDTadDTUd</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:08</t>
+          <t>HDU checksum updated 2026-01-17T12:16:38</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:08</t>
+          <t>data unit checksum updated 2026-01-17T12:16:38</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0_visda.xlsx
@@ -830,7 +830,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v3.05</t>
+          <t>v3.06</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -884,7 +884,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/05/08/2026-05-08__01-26-32_VisSci_WASP-178b_d050_n009_f11997_e000200000us.sp</t>
+          <t>/sssp/data/2026/06/30/2026-06-30__15-36-32_VisSci_WASP-18b_d050_n009_f11400_e000200000us.sp</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -920,7 +920,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WASP-178b</t>
+          <t>WASP-18b</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>227.27029418945312</t>
+          <t>24.354568481445312</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -956,7 +956,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-42.70498275756836</t>
+          <t>-45.677734375</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -974,7 +974,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>12150</t>
+          <t>11660</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -992,7 +992,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11997</t>
+          <t>11400</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1046,7 +1046,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1064,7 +1064,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1226,7 +1226,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>831518875</t>
+          <t>836149075</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1244,7 +1244,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>976000000</t>
+          <t>394000000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1262,12 +1262,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jr28Jo27Jo27Jo27</t>
+          <t>oMAepL3ZoL9boL9Z</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-06-10T14:51:12</t>
+          <t>HDU checksum updated 2026-07-15T15:21:01</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+          <t>data unit checksum updated 2026-07-15T15:21:01</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1598,12 +1598,12 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jHA9mF29jF89jF89</t>
+          <t>LIefO9deLGdeL9de</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-06-10T14:51:12</t>
+          <t>HDU checksum updated 2026-07-15T15:21:02</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1294480205</t>
+          <t>1719627190</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+          <t>data unit checksum updated 2026-07-15T15:21:02</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7lAQAj2Q9j8QAj8Q</t>
+          <t>Ae9QBe8PAe8PAe8P</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-06-10T14:51:12</t>
+          <t>HDU checksum updated 2026-07-15T15:21:02</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2014,12 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1768388195</t>
+          <t>2305784400</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+          <t>data unit checksum updated 2026-07-15T15:21:02</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11997</t>
+          <t>11400</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2358,12 +2358,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JaaLKUUIJaZIJUZI</t>
+          <t>18HM379J17GJ179J</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-06-10T14:51:12</t>
+          <t>HDU checksum updated 2026-07-15T15:21:02</t>
         </is>
       </c>
     </row>
@@ -2376,12 +2376,12 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3616581535</t>
+          <t>2113514244</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+          <t>data unit checksum updated 2026-07-15T15:21:02</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>11399</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2792,7 +2792,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>831518875.976</t>
+          <t>836149075.394</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2810,7 +2810,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>112.090637</t>
+          <t>114.74572</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2828,7 +2828,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.65043</t>
+          <t>4.114061</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2846,7 +2846,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2864,7 +2864,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2972,7 +2972,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.7882</t>
+          <t>0.7899</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2990,7 +2990,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.0003</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3008,7 +3008,7 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>27.682</t>
+          <t>140.683</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3026,7 +3026,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3044,7 +3044,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>227.268817</t>
+          <t>24.354131</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3062,7 +3062,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>6.347e-05</t>
+          <t>9.646e-05</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3080,7 +3080,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-42.705883</t>
+          <t>-45.67602</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3098,7 +3098,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3.403e-05</t>
+          <t>6.749e-05</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3116,7 +3116,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3134,7 +3134,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3152,7 +3152,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3170,7 +3170,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3188,7 +3188,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3206,7 +3206,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3224,12 +3224,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9jnIDim99imGAim9</t>
+          <t>WAAQa27NZ8ANa87N</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-06-10T14:51:12</t>
+          <t>HDU checksum updated 2026-07-15T15:21:02</t>
         </is>
       </c>
     </row>
@@ -3242,12 +3242,12 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3340827823</t>
+          <t>2735060035</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+          <t>data unit checksum updated 2026-07-15T15:21:02</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4126,12 +4126,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>9acGFTZD9YaDEYYD</t>
+          <t>KY5GNW5DKW5DKW5D</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-06-10T14:51:12</t>
+          <t>HDU checksum updated 2026-07-15T15:21:02</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3916531537</t>
+          <t>118656304</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+          <t>data unit checksum updated 2026-07-15T15:21:02</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0_visda.xlsx
@@ -884,7 +884,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/06/30/2026-06-30__15-36-32_VisSci_WASP-18b_d050_n009_f11400_e000200000us.sp</t>
+          <t>/sssp/data/2026/06/30/2026-06-30__07-32-32_VisSci_WASP-18b_d050_n009_f11400_e000200000us.sp</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1226,7 +1226,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>836149075</t>
+          <t>836120035</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1244,7 +1244,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>394000000</t>
+          <t>398000000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1262,12 +1262,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>oMAepL3ZoL9boL9Z</t>
+          <t>nNAdnK5ZnKAdnK5Z</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:21:01</t>
+          <t>HDU checksum updated 2026-07-23T15:43:14</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:21:01</t>
+          <t>data unit checksum updated 2026-07-23T15:43:14</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LIefO9deLGdeL9de</t>
+          <t>ECadE9YZECabE9WZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:21:02</t>
+          <t>HDU checksum updated 2026-07-23T15:43:14</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1719627190</t>
+          <t>1721665501</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:21:02</t>
+          <t>data unit checksum updated 2026-07-23T15:43:14</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ae9QBe8PAe8PAe8P</t>
+          <t>9a8RAa7R9a7RAa7R</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:21:02</t>
+          <t>HDU checksum updated 2026-07-23T15:43:15</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2014,12 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2305784400</t>
+          <t>2507304284</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:21:02</t>
+          <t>data unit checksum updated 2026-07-23T15:43:15</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2358,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18HM379J17GJ179J</t>
+          <t>4hI85ZH84fH84ZH8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:21:02</t>
+          <t>HDU checksum updated 2026-07-23T15:43:15</t>
         </is>
       </c>
     </row>
@@ -2376,12 +2376,12 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2113514244</t>
+          <t>3385846518</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:21:02</t>
+          <t>data unit checksum updated 2026-07-23T15:43:15</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>836149075.394</t>
+          <t>836120035.398</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2810,7 +2810,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>114.74572</t>
+          <t>114.477066</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2828,7 +2828,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.114061</t>
+          <t>4.16904</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2972,7 +2972,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.7899</t>
+          <t>0.7891</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2990,7 +2990,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3008,7 +3008,7 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>140.683</t>
+          <t>140.759</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3026,7 +3026,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0.039</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3044,7 +3044,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>24.354131</t>
+          <t>24.354337</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3062,7 +3062,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>9.646e-05</t>
+          <t>8.312e-05</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3080,7 +3080,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-45.67602</t>
+          <t>-45.676195</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3098,7 +3098,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6.749e-05</t>
+          <t>7.901e-05</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3116,7 +3116,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3152,7 +3152,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3170,7 +3170,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3188,7 +3188,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3206,7 +3206,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3224,12 +3224,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>WAAQa27NZ8ANa87N</t>
+          <t>4EJD69H94EHC49H9</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:21:02</t>
+          <t>HDU checksum updated 2026-07-23T15:43:15</t>
         </is>
       </c>
     </row>
@@ -3242,12 +3242,12 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2735060035</t>
+          <t>2025522147</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:21:02</t>
+          <t>data unit checksum updated 2026-07-23T15:43:15</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4126,12 +4126,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>KY5GNW5DKW5DKW5D</t>
+          <t>TlKLWjKLTjKLTjKL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:21:02</t>
+          <t>HDU checksum updated 2026-07-23T15:43:15</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>118656304</t>
+          <t>2612489228</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:21:02</t>
+          <t>data unit checksum updated 2026-07-23T15:43:15</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0_visda.xlsx
@@ -830,7 +830,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v3.06</t>
+          <t>v3.08</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -884,7 +884,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/06/30/2026-06-30__07-32-32_VisSci_WASP-18b_d050_n009_f11400_e000200000us.sp</t>
+          <t>/sssp/data/2026/08/15/2026-08-15__03-03-35_VisSci_HD_200654_d050_n001_f05983_e000200000us.sp</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -920,7 +920,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WASP-18b</t>
+          <t>HD_200654</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>24.354568481445312</t>
+          <t>316.64697265625</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -956,7 +956,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-45.677734375</t>
+          <t>-49.965946197509766</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -974,7 +974,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -992,7 +992,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1010,7 +1010,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1046,7 +1046,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1064,7 +1064,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1226,7 +1226,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>836120035</t>
+          <t>840078298</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1244,7 +1244,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>398000000</t>
+          <t>706000000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1262,12 +1262,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>nNAdnK5ZnKAdnK5Z</t>
+          <t>NFCDN9CANCCAN9CA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-23T15:43:14</t>
+          <t>HDU checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-23T15:43:14</t>
+          <t>data unit checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1414,7 +1414,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1428,7 +1428,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1598,12 +1598,12 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ECadE9YZECabE9WZ</t>
+          <t>MaoDOXnBManBMWnB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-23T15:43:14</t>
+          <t>HDU checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1721665501</t>
+          <t>4098491597</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-23T15:43:14</t>
+          <t>data unit checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1960,7 +1960,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1996,12 +1996,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>9a8RAa7R9a7RAa7R</t>
+          <t>3h9S5e8Q3e8Q3e8Q</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-23T15:43:15</t>
+          <t>HDU checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2014,12 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2507304284</t>
+          <t>2222157953</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-23T15:43:15</t>
+          <t>data unit checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2358,12 +2358,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4hI85ZH84fH84ZH8</t>
+          <t>eDTZeCRYeCRYeCRY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-23T15:43:15</t>
+          <t>HDU checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -2376,12 +2376,12 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3385846518</t>
+          <t>1002072366</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-23T15:43:15</t>
+          <t>data unit checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11399</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2774,12 +2774,12 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Star Det Method (UseBrightestStarsInField)</t>
+          <t>Star Det Method (ConvertRaDecToXYWithWcs)</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>836120035.398</t>
+          <t>840078298.706</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2810,7 +2810,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>114.477066</t>
+          <t>112.849083</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2828,7 +2828,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.16904</t>
+          <t>4.010312</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2900,7 +2900,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2972,7 +2972,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.7891</t>
+          <t>0.7889</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2990,7 +2990,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.0003</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3008,7 +3008,7 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>140.759</t>
+          <t>108.631</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3026,7 +3026,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.024</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3044,7 +3044,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>24.354337</t>
+          <t>316.645807</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3062,7 +3062,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>8.312e-05</t>
+          <t>6.443e-05</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3080,7 +3080,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-45.676195</t>
+          <t>-49.964709</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3098,7 +3098,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>7.901e-05</t>
+          <t>9.975e-05</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3116,7 +3116,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3134,7 +3134,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3152,7 +3152,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3170,7 +3170,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3188,7 +3188,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3206,7 +3206,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3224,12 +3224,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4EJD69H94EHC49H9</t>
+          <t>VW6DYU69VU6CVU69</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-23T15:43:15</t>
+          <t>HDU checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -3242,12 +3242,12 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2025522147</t>
+          <t>3979163444</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-23T15:43:15</t>
+          <t>data unit checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4126,12 +4126,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TlKLWjKLTjKLTjKL</t>
+          <t>fU8jfR7jfR7jfR7j</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-23T15:43:15</t>
+          <t>HDU checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2612489228</t>
+          <t>252246206</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-23T15:43:15</t>
+          <t>data unit checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0_visda.xlsx
@@ -1262,12 +1262,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NFCDN9CANCCAN9CA</t>
+          <t>NDFJQ9C9NACGN9C9</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+          <t>HDU checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:17</t>
+          <t>data unit checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MaoDOXnBManBMWnB</t>
+          <t>NaoCOVoANaoANUoA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+          <t>HDU checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:17</t>
+          <t>data unit checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3h9S5e8Q3e8Q3e8Q</t>
+          <t>4g9R5d9P4d9P4d9P</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+          <t>HDU checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:17</t>
+          <t>data unit checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2358,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>eDTZeCRYeCRYeCRY</t>
+          <t>eCTYhBSXeBSXeBSX</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+          <t>HDU checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:17</t>
+          <t>data unit checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VW6DYU69VU6CVU69</t>
+          <t>WV9BYT69WT6AWT69</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+          <t>HDU checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:17</t>
+          <t>data unit checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -4126,12 +4126,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>fU8jfR7jfR7jfR7j</t>
+          <t>fT8iiQ8ifQ8ifQ8i</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+          <t>HDU checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:17</t>
+          <t>data unit checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0_visda.xlsx
@@ -884,7 +884,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/08/15/2026-08-15__03-03-35_VisSci_HD_200654_d050_n001_f05983_e000200000us.sp</t>
+          <t>/sssp/data/2026/08/15/2026-08-15__00-16-39_VisSci_KELT-9b_d050_n005_f11916_e000200000us.sp</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -920,7 +920,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HD_200654</t>
+          <t>KELT-9b</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>316.64697265625</t>
+          <t>307.8599548339844</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -956,7 +956,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-49.965946197509766</t>
+          <t>39.9389762878418</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -974,7 +974,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -992,7 +992,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1010,7 +1010,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1046,7 +1046,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1226,7 +1226,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>840078298</t>
+          <t>840068292</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1244,7 +1244,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>706000000</t>
+          <t>8000000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1262,12 +1262,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NDFJQ9C9NACGN9C9</t>
+          <t>jCaJlAX9jAaGjAU9</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:17</t>
+          <t>HDU checksum updated 2026-09-09T15:39:20</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:17</t>
+          <t>data unit checksum updated 2026-09-09T15:39:20</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1414,7 +1414,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1428,7 +1428,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1598,12 +1598,12 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NaoCOVoANaoANUoA</t>
+          <t>epaghmVeemaeemUe</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:17</t>
+          <t>HDU checksum updated 2026-09-09T15:39:20</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4098491597</t>
+          <t>2878043978</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:17</t>
+          <t>data unit checksum updated 2026-09-09T15:39:20</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1960,7 +1960,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1996,12 +1996,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4g9R5d9P4d9P4d9P</t>
+          <t>VLS3VLR1VLR1VLR1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:17</t>
+          <t>HDU checksum updated 2026-09-09T15:39:20</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2014,12 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2222157953</t>
+          <t>17102079</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:17</t>
+          <t>data unit checksum updated 2026-09-09T15:39:20</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2358,12 +2358,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>eCTYhBSXeBSXeBSX</t>
+          <t>H7omH5okH5okH5ok</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:17</t>
+          <t>HDU checksum updated 2026-09-09T15:39:20</t>
         </is>
       </c>
     </row>
@@ -2376,12 +2376,12 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1002072366</t>
+          <t>2032871319</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:17</t>
+          <t>data unit checksum updated 2026-09-09T15:39:20</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>11915</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2792,7 +2792,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>840078298.706</t>
+          <t>840068292.008</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2810,7 +2810,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>112.849083</t>
+          <t>189.042358</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2828,7 +2828,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.010312</t>
+          <t>19.295027</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2846,7 +2846,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2864,7 +2864,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2972,7 +2972,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.7889</t>
+          <t>0.7899</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2990,7 +2990,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.0003</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3008,7 +3008,7 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>108.631</t>
+          <t>247.711</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3026,7 +3026,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3044,7 +3044,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>316.645807</t>
+          <t>307.860376</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3062,7 +3062,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>6.443e-05</t>
+          <t>8.489e-05</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3080,7 +3080,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-49.964709</t>
+          <t>39.939956</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3098,7 +3098,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>9.975e-05</t>
+          <t>6.817e-05</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3116,7 +3116,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3134,7 +3134,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3152,7 +3152,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3170,7 +3170,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>102</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3188,7 +3188,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3206,7 +3206,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3224,12 +3224,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>WV9BYT69WT6AWT69</t>
+          <t>UAK5aAJ5XAJ5aAJ5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:17</t>
+          <t>HDU checksum updated 2026-09-09T15:39:20</t>
         </is>
       </c>
     </row>
@@ -3242,12 +3242,12 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3979163444</t>
+          <t>1301764915</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:17</t>
+          <t>data unit checksum updated 2026-09-09T15:39:20</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4126,12 +4126,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>fT8iiQ8ifQ8ifQ8i</t>
+          <t>5QLbAOJb8OJbAOJb</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:17</t>
+          <t>HDU checksum updated 2026-09-09T15:39:20</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>252246206</t>
+          <t>632362844</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:17</t>
+          <t>data unit checksum updated 2026-09-09T15:39:20</t>
         </is>
       </c>
     </row>
